--- a/jogos_2026-07-01.xlsx
+++ b/jogos_2026-07-01.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>

--- a/jogos_2026-07-01.xlsx
+++ b/jogos_2026-07-01.xlsx
@@ -734,55 +734,55 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>

--- a/jogos_2026-07-01.xlsx
+++ b/jogos_2026-07-01.xlsx
@@ -734,55 +734,55 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="R2" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="S2" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.75</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.59</v>
       </c>
       <c r="V2" t="n">
         <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>

--- a/jogos_2026-07-01.xlsx
+++ b/jogos_2026-07-01.xlsx
@@ -746,43 +746,43 @@
         <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="AA2" t="n">
         <v>1.86</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC2" t="n">
         <v>3.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF2" t="n">
         <v>1.65</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>

--- a/jogos_2026-07-01.xlsx
+++ b/jogos_2026-07-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU4"/>
+  <dimension ref="A1:AU5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,6 +1147,165 @@
       </c>
       <c r="AU4" s="3" t="n">
         <v>46204.70833333334</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>LDU Quito</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Orense SC</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="3" t="n">
+        <v>46204.79166666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-07-01.xlsx
+++ b/jogos_2026-07-01.xlsx
@@ -737,13 +737,13 @@
         <v>2.75</v>
       </c>
       <c r="R2" t="n">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="S2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T2" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="U2" t="n">
         <v>2.67</v>
@@ -758,16 +758,16 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AC2" t="n">
         <v>3.15</v>
@@ -779,7 +779,7 @@
         <v>1.07</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG2" t="n">
         <v>2.02</v>
@@ -798,7 +798,7 @@
         <v>1.24</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1211,7 +1211,7 @@
         <v>5.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="R5" t="n">
         <v>2.3</v>
@@ -1229,28 +1229,28 @@
         <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
         <v>3.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
         <v>1.11</v>

--- a/jogos_2026-07-01.xlsx
+++ b/jogos_2026-07-01.xlsx
@@ -776,7 +776,7 @@
         <v>1.28</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF2" t="n">
         <v>1.68</v>
@@ -1244,7 +1244,7 @@
         <v>1.98</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AC5" t="n">
         <v>3.8</v>
@@ -1259,7 +1259,7 @@
         <v>1.95</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AK5" t="n">
         <v>2.7</v>

--- a/jogos_2026-07-01.xlsx
+++ b/jogos_2026-07-01.xlsx
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q2" t="n">
         <v>2.75</v>
       </c>
       <c r="R2" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="S2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T2" t="n">
         <v>2.79</v>
@@ -764,10 +764,10 @@
         <v>3.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AC2" t="n">
         <v>3.15</v>
@@ -776,7 +776,7 @@
         <v>1.28</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF2" t="n">
         <v>1.68</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>

--- a/jogos_2026-07-01.xlsx
+++ b/jogos_2026-07-01.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="O3" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="P3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="O5" t="n">
         <v>4.2</v>
@@ -1211,7 +1211,7 @@
         <v>5.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="R5" t="n">
         <v>2.3</v>
@@ -1220,7 +1220,7 @@
         <v>1.33</v>
       </c>
       <c r="T5" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="U5" t="n">
         <v>2.88</v>
@@ -1244,22 +1244,22 @@
         <v>1.98</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
         <v>3.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>

--- a/jogos_2026-07-01.xlsx
+++ b/jogos_2026-07-01.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="O3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="P3" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="P4" t="n">
         <v>2.48</v>

--- a/jogos_2026-07-01.xlsx
+++ b/jogos_2026-07-01.xlsx
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="O2" t="n">
         <v>3.28</v>
       </c>
       <c r="P2" t="n">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="Q2" t="n">
         <v>2.75</v>
       </c>
       <c r="R2" t="n">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="S2" t="n">
         <v>1.34</v>
@@ -746,10 +746,10 @@
         <v>2.79</v>
       </c>
       <c r="U2" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="V2" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
         <v>1.05</v>
@@ -767,19 +767,19 @@
         <v>1.86</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
         <v>3.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE2" t="n">
         <v>1.07</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG2" t="n">
         <v>2.02</v>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK2" t="n">
         <v>1.56</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="O3" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="P3" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AB3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF3" t="n">
         <v>2</v>
       </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1211,7 +1211,7 @@
         <v>5.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="R5" t="n">
         <v>2.3</v>
@@ -1220,16 +1220,16 @@
         <v>1.33</v>
       </c>
       <c r="T5" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="U5" t="n">
         <v>2.88</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
@@ -1238,28 +1238,28 @@
         <v>1.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.2</v>
+        <v>3.71</v>
       </c>
       <c r="AA5" t="n">
         <v>1.98</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC5" t="n">
         <v>3.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>

--- a/jogos_2026-07-01.xlsx
+++ b/jogos_2026-07-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU5"/>
+  <dimension ref="A1:AU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,27 +678,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -828,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>46204.5</v>
+        <v>46204.375</v>
       </c>
     </row>
     <row r="3">
@@ -837,27 +837,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -987,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="AU3" s="3" t="n">
-        <v>46204.58333333334</v>
+        <v>46204.375</v>
       </c>
     </row>
     <row r="4">
@@ -996,12 +996,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T4" t="n">
         <v>2.79</v>
       </c>
-      <c r="O4" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>46204.70833333334</v>
+        <v>46204.5</v>
       </c>
     </row>
     <row r="5">
@@ -1155,157 +1155,793 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ethiopia Ethiopia Premier League</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Fasil Ketema</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ethiopian Medhin</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="3" t="n">
+        <v>46204.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Canada Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Forge FC</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vancouver FC</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="3" t="n">
+        <v>46204.58333333334</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Canada Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>HFX Wanderers FC</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Atlético Ottawa</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="3" t="n">
+        <v>46204.70833333334</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>LDU Quito</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Orense SC</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>suspended</t>
         </is>
       </c>
-      <c r="N5" t="n">
+      <c r="N8" t="n">
         <v>1.45</v>
       </c>
-      <c r="O5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="O8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P8" t="n">
         <v>5.75</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q8" t="n">
         <v>1.95</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R8" t="n">
         <v>2.3</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S8" t="n">
         <v>1.33</v>
       </c>
-      <c r="T5" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="U5" t="n">
+      <c r="T8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="U8" t="n">
         <v>2.88</v>
       </c>
-      <c r="V5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="V8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Y8" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z5" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="AA5" t="n">
+      <c r="Z8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA8" t="n">
         <v>1.98</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AB8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC8" t="n">
         <v>3.8</v>
       </c>
-      <c r="AD5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE5" t="n">
+      <c r="AD8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.05</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AF8" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AG8" t="n">
         <v>1.66</v>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" s="3" t="n">
+      <c r="AJ8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="3" t="n">
         <v>46204.79166666666</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Delfin SC</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="3" t="n">
+        <v>46204.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-07-01.xlsx
+++ b/jogos_2026-07-01.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>

--- a/jogos_2026-07-01.xlsx
+++ b/jogos_2026-07-01.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">

--- a/jogos_2026-07-01.xlsx
+++ b/jogos_2026-07-01.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,34 +1361,34 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="O6" t="n">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="P6" t="n">
-        <v>5.5</v>
+        <v>5.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="R6" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S6" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T6" t="n">
-        <v>2.75</v>
+        <v>2.97</v>
       </c>
       <c r="U6" t="n">
-        <v>2.88</v>
+        <v>2.51</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
@@ -1397,28 +1397,28 @@
         <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE6" t="n">
         <v>1.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.79</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
-        <v>3.24</v>
+        <v>2.9</v>
       </c>
       <c r="P7" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="O8" t="n">
         <v>3.8</v>
@@ -1694,7 +1694,7 @@
         <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T8" t="n">
         <v>2.78</v>
@@ -1709,16 +1709,16 @@
         <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
         <v>1.31</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AB8" t="n">
         <v>1.8</v>
@@ -1727,16 +1727,16 @@
         <v>3.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE8" t="n">
         <v>1.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK8" t="n">
         <v>2.7</v>
@@ -1838,25 +1838,25 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="O9" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="P9" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
         <v>3.3</v>
       </c>
       <c r="R9" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="T9" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="U9" t="n">
         <v>3.28</v>
@@ -1868,7 +1868,7 @@
         <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Y9" t="n">
         <v>1.48</v>
@@ -1877,22 +1877,22 @@
         <v>2.43</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.56</v>
+        <v>4.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AG9" t="n">
         <v>1.73</v>

--- a/jogos_2026-07-01.xlsx
+++ b/jogos_2026-07-01.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O4" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="P4" t="n">
-        <v>3.01</v>
+        <v>3.16</v>
       </c>
       <c r="Q4" t="n">
         <v>2.75</v>
       </c>
       <c r="R4" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T4" t="n">
-        <v>2.79</v>
+        <v>2.67</v>
       </c>
       <c r="U4" t="n">
         <v>2.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
         <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>3.15</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF4" t="n">
         <v>1.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="O6" t="n">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="P6" t="n">
-        <v>5.26</v>
+        <v>5.7</v>
       </c>
       <c r="Q6" t="n">
         <v>1.91</v>
@@ -1376,49 +1376,49 @@
         <v>2.3</v>
       </c>
       <c r="S6" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>2.97</v>
+        <v>2.79</v>
       </c>
       <c r="U6" t="n">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.75</v>
+        <v>2.65</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB6" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.49</v>
+        <v>2.23</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="O7" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="S7" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U7" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
         <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
         <v>3.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="O8" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="Q8" t="n">
         <v>1.95</v>
@@ -1697,46 +1697,46 @@
         <v>1.34</v>
       </c>
       <c r="T8" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="U8" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.31</v>
+        <v>3.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1838,22 +1838,22 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="O9" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R9" t="n">
         <v>1.91</v>
       </c>
       <c r="S9" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T9" t="n">
         <v>2.45</v>
@@ -1865,28 +1865,28 @@
         <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.8</v>
+        <v>5.64</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AE9" t="n">
         <v>1.05</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-07-01.xlsx
+++ b/jogos_2026-07-01.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="O2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P2" t="n">
         <v>2.65</v>
       </c>
-      <c r="P2" t="n">
-        <v>2.95</v>
-      </c>
       <c r="Q2" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="O3" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="P3" t="n">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>3.24</v>
+        <v>2.8</v>
       </c>
       <c r="P4" t="n">
-        <v>3.16</v>
+        <v>2.28</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="O5" t="n">
-        <v>2.8</v>
+        <v>3.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.28</v>
+        <v>3.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1675,17 +1675,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="O8" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q8" t="n">
         <v>1.95</v>
@@ -1712,22 +1712,22 @@
         <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
         <v>3.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
         <v>3.68</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE8" t="n">
         <v>1.11</v>
@@ -1736,7 +1736,7 @@
         <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1838,61 +1838,61 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="P9" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="R9" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="S9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.5</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AC9" t="n">
-        <v>5.64</v>
+        <v>5.79</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE9" t="n">
         <v>1.05</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="AG9" t="n">
         <v>1.73</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-07-01.xlsx
+++ b/jogos_2026-07-01.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O2" t="n">
         <v>2.7</v>
       </c>
-      <c r="O2" t="n">
-        <v>2.8</v>
-      </c>
       <c r="P2" t="n">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,139 +852,139 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.52</v>
+        <v>1.63</v>
       </c>
       <c r="O3" t="n">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="P3" t="n">
-        <v>2.95</v>
+        <v>4.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57', '81']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46204.375</v>

--- a/jogos_2026-07-01.xlsx
+++ b/jogos_2026-07-01.xlsx
@@ -693,139 +693,139 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.5</v>
+        <v>1.63</v>
       </c>
       <c r="O2" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2.87</v>
+        <v>4.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>['57', '81']</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
         <v>6</v>
       </c>
-      <c r="AD2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AK2" t="n">
+      <c r="AN2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AR2" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46204.375</v>
@@ -852,139 +852,139 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>['19', '27', '59']</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN3" t="n">
         <v>2</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="O3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>['57', '81']</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>['36']</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>3</v>
-      </c>
       <c r="AO3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AP3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.66</v>
+        <v>1.15</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AS3" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="AT3" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46204.375</v>
@@ -1179,66 +1179,66 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="O5" t="n">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>3.16</v>
+        <v>3.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R5" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="S5" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T5" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
         <v>2.75</v>
       </c>
       <c r="V5" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
         <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="AA5" t="n">
         <v>1.85</v>
@@ -1250,29 +1250,29 @@
         <v>3.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+2', '48']</t>
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK5" t="n">
         <v>1.52</v>
@@ -1281,28 +1281,28 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46204.5</v>
@@ -1367,58 +1367,58 @@
         <v>4.25</v>
       </c>
       <c r="P6" t="n">
-        <v>5.7</v>
+        <v>5.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T6" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="U6" t="n">
         <v>2.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AC6" t="n">
         <v>2.91</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P7" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R7" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T7" t="n">
-        <v>2.6</v>
+        <v>3.06</v>
       </c>
       <c r="U7" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="V7" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,16 +1679,16 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="O8" t="n">
         <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>5.75</v>
+        <v>5.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="R8" t="n">
         <v>2.3</v>
@@ -1697,13 +1697,13 @@
         <v>1.34</v>
       </c>
       <c r="T8" t="n">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="U8" t="n">
         <v>2.75</v>
       </c>
       <c r="V8" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
         <v>1.06</v>
@@ -1712,22 +1712,22 @@
         <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
         <v>3.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.68</v>
+        <v>3.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
         <v>1.11</v>
@@ -1736,7 +1736,7 @@
         <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1838,22 +1838,22 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="P9" t="n">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.55</v>
+        <v>3.61</v>
       </c>
       <c r="R9" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="S9" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="T9" t="n">
         <v>2.4</v>
@@ -1865,10 +1865,10 @@
         <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
         <v>1.53</v>
@@ -1883,10 +1883,10 @@
         <v>1.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.79</v>
+        <v>6.54</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
         <v>1.05</v>
@@ -1911,7 +1911,7 @@
         <v>1.33</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-07-01.xlsx
+++ b/jogos_2026-07-01.xlsx
@@ -693,139 +693,139 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>['19', '27', '59']</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN2" t="n">
         <v>2</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="O2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>['57', '81']</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>['36']</t>
-        </is>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>3</v>
-      </c>
       <c r="AO2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AP2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.66</v>
+        <v>1.15</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AS2" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="AT2" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46204.375</v>
@@ -852,139 +852,139 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>['57', '81']</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN3" t="n">
         <v>3</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>['19', '27', '59']</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AK3" t="n">
+      <c r="AO3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AR3" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AS3" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="AT3" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46204.375</v>
@@ -1001,149 +1001,149 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>2.11</v>
       </c>
       <c r="O4" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>2.28</v>
+        <v>3.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+2', '48']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46204.5</v>
@@ -1160,149 +1160,149 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.11</v>
+        <v>3.2</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="P5" t="n">
-        <v>3.02</v>
+        <v>2.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>['45+2', '48']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AN5" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="AO5" t="n">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="AP5" t="n">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46204.5</v>
@@ -1338,26 +1338,26 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['61', '64', '75']</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '45+2']</t>
         </is>
       </c>
       <c r="AJ6" t="n">
@@ -1440,28 +1440,28 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN6" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46204.58333333334</v>
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="O7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="R7" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S7" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T7" t="n">
-        <v>3.06</v>
+        <v>2.83</v>
       </c>
       <c r="U7" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="V7" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-07-01.xlsx
+++ b/jogos_2026-07-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU9"/>
+  <dimension ref="A1:AU8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1497,26 +1497,26 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['68']</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '26', '36']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
@@ -1599,28 +1599,28 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN7" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46204.70833333334</v>
@@ -1697,62 +1697,62 @@
         <v>1.34</v>
       </c>
       <c r="T8" t="n">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="U8" t="n">
         <v>2.75</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W8" t="n">
         <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
         <v>3.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.11</v>
       </c>
-      <c r="AF8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AK8" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1783,165 +1783,6 @@
       </c>
       <c r="AU8" s="3" t="n">
         <v>46204.79166666666</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Delfin SC</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>CS Emelec</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" s="3" t="n">
-        <v>46204.875</v>
       </c>
     </row>
   </sheetData>
